--- a/data/OP_pop_data.xlsx
+++ b/data/OP_pop_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dcgovict-my.sharepoint.com/personal/edward_rodrigue_dc_gov/Documents/Documents/GitHub/youth-stats/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\GitHub\youth-stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_F25DC773A252ABDACC10481B3999495A5ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB4CF059-B64C-4B41-9BBF-70F174786D49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0A917B-488A-4996-95EB-2D420A150EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>https://planning.dc.gov/sites/default/files/dc/sites/op/publication/attachments/DCOP_SDC_June%25202010%2520Briefing%2520Report.pdf</t>
   </si>
@@ -57,7 +57,13 @@
     <t>u15_pct</t>
   </si>
   <si>
-    <t>I added the year 2025 based on ACS data.</t>
+    <t>I added the year 2025 based on Census/KidsCount data:</t>
+  </si>
+  <si>
+    <t>https://datacenter.aecf.org/data/tables/101-child-population-by-age-group?loc=10&amp;loct=3#detailed/3/any/false/575/62,63,64,4693/419,420</t>
+  </si>
+  <si>
+    <t>https://datacenter.aecf.org/data/tables/99-total-population-by-child-and-adult-populations?loc=10&amp;loct=3#detailed/3/any/false/575/39,40,41/416,417</t>
   </si>
 </sst>
 </file>
@@ -377,9 +383,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -393,7 +399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -408,7 +414,7 @@
         <v>0.15405430731858516</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2009</v>
       </c>
@@ -424,7 +430,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -440,7 +446,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1990</v>
       </c>
@@ -458,7 +464,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>1980</v>
       </c>
@@ -475,7 +481,7 @@
       <c r="E6" s="1"/>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>1970</v>
       </c>
@@ -492,7 +498,7 @@
       <c r="E7" s="1"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>1960</v>
       </c>
@@ -509,7 +515,7 @@
       <c r="E8" s="1"/>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>1950</v>
       </c>
@@ -526,7 +532,7 @@
       <c r="E9" s="1"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1940</v>
       </c>
@@ -543,7 +549,7 @@
       <c r="E10" s="1"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>1930</v>
       </c>
@@ -560,7 +566,7 @@
       <c r="E11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>1920</v>
       </c>
@@ -577,7 +583,7 @@
       <c r="E12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>1910</v>
       </c>
@@ -594,7 +600,7 @@
       <c r="E13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>1900</v>
       </c>
@@ -611,19 +617,19 @@
       <c r="E14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="14:14" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="14:14" x14ac:dyDescent="0.55000000000000004">
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.55000000000000004">
       <c r="N19" s="1"/>
     </row>
   </sheetData>
@@ -633,22 +639,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D10BE9A-23C7-4419-849A-0212BE943E50}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
